--- a/东鹏饮料研究/data/东鹏饮料_财务数据与指标_2020_2024.xlsx
+++ b/东鹏饮料研究/data/东鹏饮料_财务数据与指标_2020_2024.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>322567166.2</v>
+        <v>102807308.82</v>
       </c>
       <c r="D5" t="n">
         <v>90980455.62</v>
@@ -699,7 +699,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1909130073.15</v>
+        <v>1926155822.8</v>
       </c>
       <c r="D13" t="n">
         <v>616703752.21</v>
@@ -1113,9 +1113,11 @@
           <t>租赁负债</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
-        <v>13117385.26</v>
+        <v>94317364.27</v>
       </c>
       <c r="D32" t="n">
         <v>85244622.44</v>
@@ -1316,13 +1318,13 @@
         <v>25825000</v>
       </c>
       <c r="D41" t="n">
-        <v>85244622.44</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>95386367.7</v>
+        <v>220000000</v>
       </c>
       <c r="F41" t="n">
-        <v>85454382.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1469,16 +1471,16 @@
         <v>617500</v>
       </c>
       <c r="C2" t="n">
-        <v>-785034.4399999999</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-358141.05</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-1692419.58</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-957927.08</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1489,7 +1491,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>-785034.4399999999</v>
+        <v>116670089.93</v>
       </c>
       <c r="D3" t="n">
         <v>12787831.1</v>
@@ -1794,7 +1796,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>812063500</v>
       </c>
       <c r="C17" t="n">
         <v>1192960407.59</v>
@@ -1951,16 +1953,16 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>1528557304.56</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-2234206</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>-8506.200000000001</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>-98089.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1971,7 +1973,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>1528557304.56</v>
+        <v>1016701.83</v>
       </c>
       <c r="D25" t="n">
         <v>-2234206</v>
